--- a/source_data/workbooks/Source_Data_Fig2.xlsx
+++ b/source_data/workbooks/Source_Data_Fig2.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="98">
   <si>
     <t>plot_order</t>
   </si>
@@ -107,10 +107,7 @@
     <t>NOVA</t>
   </si>
   <si>
-    <t>TLAgent-removing knowledge</t>
-  </si>
-  <si>
-    <t>TLAgent</t>
+    <t>TissueLab</t>
   </si>
   <si>
     <t>pearson</t>
@@ -146,9 +143,6 @@
     <t>0.0574</t>
   </si>
   <si>
-    <t>0.5117</t>
-  </si>
-  <si>
     <t>0.8425</t>
   </si>
   <si>
@@ -207,12 +201,6 @@
   </si>
   <si>
     <t>32.1446</t>
-  </si>
-  <si>
-    <t>3.2945</t>
-  </si>
-  <si>
-    <t>4.7438</t>
   </si>
   <si>
     <t>2.0738</t>
@@ -655,13 +643,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -743,10 +731,10 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
         <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
       </c>
       <c r="H2">
         <v>105</v>
@@ -761,7 +749,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -781,10 +769,10 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
         <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
       </c>
       <c r="H3">
         <v>105</v>
@@ -799,7 +787,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -834,10 +822,10 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
       </c>
       <c r="H4">
         <v>105</v>
@@ -852,7 +840,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M4">
         <v>0.2367</v>
@@ -887,10 +875,10 @@
         <v>23</v>
       </c>
       <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
       </c>
       <c r="H5">
         <v>105</v>
@@ -905,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M5">
         <v>0.0453</v>
@@ -940,10 +928,10 @@
         <v>24</v>
       </c>
       <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
       </c>
       <c r="H6">
         <v>105</v>
@@ -958,7 +946,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M6">
         <v>0.1194</v>
@@ -993,10 +981,10 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
       </c>
       <c r="H7">
         <v>105</v>
@@ -1011,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M7">
         <v>0.08459999999999999</v>
@@ -1046,10 +1034,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
       </c>
       <c r="H8">
         <v>105</v>
@@ -1064,7 +1052,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M8">
         <v>0.0988</v>
@@ -1099,10 +1087,10 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
         <v>31</v>
-      </c>
-      <c r="G9" t="s">
-        <v>32</v>
       </c>
       <c r="H9">
         <v>105</v>
@@ -1117,7 +1105,7 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M9">
         <v>0.1091</v>
@@ -1152,10 +1140,10 @@
         <v>28</v>
       </c>
       <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
         <v>31</v>
-      </c>
-      <c r="G10" t="s">
-        <v>32</v>
       </c>
       <c r="H10">
         <v>105</v>
@@ -1170,7 +1158,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M10">
         <v>0.1251</v>
@@ -1205,10 +1193,10 @@
         <v>29</v>
       </c>
       <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
         <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>32</v>
       </c>
       <c r="H11">
         <v>105</v>
@@ -1223,74 +1211,21 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <v>0.365</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="O11">
-        <v>0.6598000000000001</v>
+        <v>0.9124</v>
       </c>
       <c r="P11">
-        <v>0.3494</v>
+        <v>0.7025</v>
       </c>
       <c r="Q11">
-        <v>0.6676</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12">
-        <v>105</v>
-      </c>
-      <c r="I12">
-        <v>43</v>
-      </c>
-      <c r="J12">
-        <v>105</v>
-      </c>
-      <c r="K12">
-        <v>5</v>
-      </c>
-      <c r="L12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0.7233000000000001</v>
-      </c>
-      <c r="O12">
-        <v>0.9124</v>
-      </c>
-      <c r="P12">
-        <v>0.7025</v>
-      </c>
-      <c r="Q12">
         <v>0.9193</v>
       </c>
     </row>
@@ -1301,13 +1236,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -1377,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1389,10 +1324,10 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>105</v>
@@ -1407,7 +1342,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -1415,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -1427,10 +1362,10 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>105</v>
@@ -1445,7 +1380,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -1453,7 +1388,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -1465,10 +1400,10 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4">
         <v>105</v>
@@ -1483,7 +1418,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -1506,7 +1441,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -1518,10 +1453,10 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <v>105</v>
@@ -1536,7 +1471,7 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1559,7 +1494,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -1571,10 +1506,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6">
         <v>105</v>
@@ -1589,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M6">
         <v>107.2838</v>
@@ -1612,7 +1547,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -1624,10 +1559,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>105</v>
@@ -1642,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M7">
         <v>520.1459</v>
@@ -1665,7 +1600,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -1677,10 +1612,10 @@
         <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H8">
         <v>105</v>
@@ -1695,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M8">
         <v>0.0574</v>
@@ -1718,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -1730,10 +1665,10 @@
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9">
         <v>105</v>
@@ -1748,7 +1683,7 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M9">
         <v>0.6035</v>
@@ -1771,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -1783,10 +1718,10 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10">
         <v>105</v>
@@ -1801,7 +1736,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M10">
         <v>0.07290000000000001</v>
@@ -1824,7 +1759,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -1836,10 +1771,10 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11">
         <v>105</v>
@@ -1854,7 +1789,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M11">
         <v>0.2261</v>
@@ -1877,7 +1812,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -1889,10 +1824,10 @@
         <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H12">
         <v>105</v>
@@ -1907,7 +1842,7 @@
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M12">
         <v>0.1144</v>
@@ -1930,7 +1865,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -1942,10 +1877,10 @@
         <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H13">
         <v>105</v>
@@ -1960,7 +1895,7 @@
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M13">
         <v>0.1923</v>
@@ -1983,7 +1918,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -1995,10 +1930,10 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H14">
         <v>105</v>
@@ -2013,7 +1948,7 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M14">
         <v>0.1446</v>
@@ -2036,7 +1971,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
@@ -2048,10 +1983,10 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H15">
         <v>105</v>
@@ -2066,7 +2001,7 @@
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M15">
         <v>0.2591</v>
@@ -2089,7 +2024,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -2101,10 +2036,10 @@
         <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16">
         <v>105</v>
@@ -2119,7 +2054,7 @@
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M16">
         <v>0.3525</v>
@@ -2142,7 +2077,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -2154,10 +2089,10 @@
         <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H17">
         <v>105</v>
@@ -2172,7 +2107,7 @@
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M17">
         <v>1.0431</v>
@@ -2195,7 +2130,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -2207,10 +2142,10 @@
         <v>28</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18">
         <v>105</v>
@@ -2225,7 +2160,7 @@
         <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M18">
         <v>3.2857</v>
@@ -2248,7 +2183,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -2260,10 +2195,10 @@
         <v>28</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H19">
         <v>105</v>
@@ -2278,7 +2213,7 @@
         <v>5</v>
       </c>
       <c r="L19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M19">
         <v>24.3333</v>
@@ -2301,7 +2236,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
@@ -2313,10 +2248,10 @@
         <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H20">
         <v>105</v>
@@ -2331,22 +2266,22 @@
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
       <c r="N20">
-        <v>2.6749</v>
+        <v>1.6596</v>
       </c>
       <c r="O20">
-        <v>3.982</v>
+        <v>2.5277</v>
       </c>
       <c r="P20">
-        <v>2.6242</v>
+        <v>1.5889</v>
       </c>
       <c r="Q20">
-        <v>4.0591</v>
+        <v>2.644</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -2354,7 +2289,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -2366,10 +2301,10 @@
         <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H21">
         <v>105</v>
@@ -2384,127 +2319,21 @@
         <v>5</v>
       </c>
       <c r="L21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
       <c r="N21">
-        <v>3.6718</v>
+        <v>2.4862</v>
       </c>
       <c r="O21">
-        <v>5.9081</v>
+        <v>3.6644</v>
       </c>
       <c r="P21">
-        <v>3.5906</v>
+        <v>2.4321</v>
       </c>
       <c r="Q21">
-        <v>5.9904</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22">
-        <v>105</v>
-      </c>
-      <c r="I22">
-        <v>43</v>
-      </c>
-      <c r="J22">
-        <v>105</v>
-      </c>
-      <c r="K22">
-        <v>5</v>
-      </c>
-      <c r="L22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>1.6596</v>
-      </c>
-      <c r="O22">
-        <v>2.5277</v>
-      </c>
-      <c r="P22">
-        <v>1.5889</v>
-      </c>
-      <c r="Q22">
-        <v>2.644</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23">
-        <v>105</v>
-      </c>
-      <c r="I23">
-        <v>43</v>
-      </c>
-      <c r="J23">
-        <v>105</v>
-      </c>
-      <c r="K23">
-        <v>5</v>
-      </c>
-      <c r="L23" t="s">
-        <v>66</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>2.4862</v>
-      </c>
-      <c r="O23">
-        <v>3.6644</v>
-      </c>
-      <c r="P23">
-        <v>2.4321</v>
-      </c>
-      <c r="Q23">
         <v>3.7549</v>
       </c>
     </row>
@@ -2592,22 +2421,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H2">
         <v>321</v>
@@ -2622,7 +2451,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2630,22 +2459,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H3">
         <v>321</v>
@@ -2660,7 +2489,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -2683,22 +2512,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H4">
         <v>321</v>
@@ -2713,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M4">
         <v>0.0031</v>
@@ -2736,22 +2565,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H5">
         <v>321</v>
@@ -2766,7 +2595,7 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M5">
         <v>0.0195</v>
@@ -2789,22 +2618,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H6">
         <v>321</v>
@@ -2819,7 +2648,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M6">
         <v>0.0065</v>
@@ -2842,22 +2671,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H7">
         <v>321</v>
@@ -2872,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="M7">
         <v>0.0223</v>
@@ -2895,22 +2724,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H8">
         <v>321</v>
@@ -2925,7 +2754,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M8">
         <v>0.008200000000000001</v>
@@ -2948,22 +2777,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H9">
         <v>321</v>
@@ -2978,7 +2807,7 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M9">
         <v>0.0274</v>
@@ -3001,22 +2830,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H10">
         <v>321</v>
@@ -3031,7 +2860,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M10">
         <v>0.0199</v>
@@ -3054,22 +2883,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
         <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
       </c>
       <c r="H11">
         <v>321</v>
@@ -3084,7 +2913,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -3185,22 +3014,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H2">
         <v>321</v>
@@ -3215,7 +3044,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -3223,22 +3052,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H3">
         <v>321</v>
@@ -3253,7 +3082,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -3276,22 +3105,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H4">
         <v>321</v>
@@ -3306,7 +3135,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M4">
         <v>0.0028</v>
@@ -3329,22 +3158,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H5">
         <v>321</v>
@@ -3359,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M5">
         <v>0.0235</v>
@@ -3382,22 +3211,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H6">
         <v>321</v>
@@ -3412,7 +3241,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M6">
         <v>0.0048</v>
@@ -3435,22 +3264,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H7">
         <v>321</v>
@@ -3465,7 +3294,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M7">
         <v>0.0193</v>
@@ -3488,22 +3317,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H8">
         <v>321</v>
@@ -3518,7 +3347,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M8">
         <v>0.0094</v>
@@ -3541,22 +3370,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H9">
         <v>321</v>
@@ -3571,7 +3400,7 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M9">
         <v>0.0162</v>
@@ -3594,22 +3423,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H10">
         <v>321</v>
@@ -3624,7 +3453,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M10">
         <v>0.0135</v>
@@ -3647,22 +3476,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H11">
         <v>321</v>
@@ -3677,7 +3506,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -3779,22 +3608,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
       <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
         <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
       </c>
       <c r="H2">
         <v>321</v>
@@ -3809,7 +3638,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -3817,22 +3646,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
         <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
       </c>
       <c r="H3">
         <v>321</v>
@@ -3847,7 +3676,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -3870,22 +3699,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
       </c>
       <c r="H4">
         <v>321</v>
@@ -3900,7 +3729,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M4">
         <v>0.042</v>
@@ -3923,22 +3752,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
       </c>
       <c r="H5">
         <v>321</v>
@@ -3953,7 +3782,7 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M5">
         <v>0.0218</v>
@@ -3976,22 +3805,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
       </c>
       <c r="H6">
         <v>321</v>
@@ -4006,7 +3835,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M6">
         <v>0.0269</v>
@@ -4029,22 +3858,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
       </c>
       <c r="H7">
         <v>321</v>
@@ -4059,7 +3888,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M7">
         <v>0.0261</v>
@@ -4082,22 +3911,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
       </c>
       <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
       </c>
       <c r="H8">
         <v>321</v>
@@ -4112,7 +3941,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M8">
         <v>0.0349</v>
@@ -4135,22 +3964,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
       </c>
       <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
         <v>31</v>
-      </c>
-      <c r="G9" t="s">
-        <v>32</v>
       </c>
       <c r="H9">
         <v>321</v>
@@ -4165,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M9">
         <v>0.0425</v>
@@ -4188,22 +4017,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
       </c>
       <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
         <v>31</v>
-      </c>
-      <c r="G10" t="s">
-        <v>32</v>
       </c>
       <c r="H10">
         <v>321</v>
@@ -4218,7 +4047,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M10">
         <v>0.0427</v>
@@ -4241,22 +4070,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
         <v>30</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>32</v>
       </c>
       <c r="H11">
         <v>321</v>
@@ -4271,7 +4100,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M11">
         <v>0</v>
